--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,22 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\DSDA11\N322\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDB71A0-7974-46C0-9108-B584FEC9B15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6D2148-BD7D-46A1-9899-41F0E4576B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMartDataset" sheetId="1" r:id="rId1"/>
     <sheet name="FlashFill" sheetId="3" r:id="rId2"/>
     <sheet name="CustomList" sheetId="4" r:id="rId3"/>
     <sheet name="Lookup" sheetId="12" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="8" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="9" r:id="rId7"/>
-    <sheet name="Sheet5" sheetId="10" r:id="rId8"/>
+    <sheet name="HLOOKUP" sheetId="13" r:id="rId5"/>
+    <sheet name="Indirect" sheetId="14" r:id="rId6"/>
+    <sheet name="Data Validation" sheetId="15" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId10"/>
+    <sheet name="Sheet5" sheetId="10" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$1:$A$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Sheet1!$A$1:$A$7</definedName>
     <definedName name="category">Table2[Category]</definedName>
     <definedName name="customerType">Table2[customer_type]</definedName>
     <definedName name="discount">Table2[discount]</definedName>
@@ -36,14 +39,14 @@
   <calcPr calcId="191029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4247" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4279" uniqueCount="711">
   <si>
     <t>Region</t>
   </si>
@@ -2173,6 +2176,60 @@
   <si>
     <t>Using Index-Match</t>
   </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Using VLOOKUP</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>12as</t>
+  </si>
+  <si>
+    <t>AS64</t>
+  </si>
+  <si>
+    <t>dd43</t>
+  </si>
 </sst>
 </file>
 
@@ -2182,11 +2239,25 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2319,7 +2390,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2380,8 +2451,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2495,126 +2572,582 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="40">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2676,32 +3209,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -2713,34 +3220,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2786,16 +3265,17 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2839,16 +3319,17 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2876,139 +3357,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3053,33 +3401,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
@@ -3092,32 +3413,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3161,32 +3456,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3198,33 +3467,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3269,32 +3511,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3306,32 +3522,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3375,16 +3565,17 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3412,87 +3603,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3592,26 +3702,26 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5BA5497F-DEC0-44AB-8F20-80EF69812EB7}" name="Table2" displayName="Table2" ref="A1:P500" totalsRowCount="1" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="A1:P499" xr:uid="{5BA5497F-DEC0-44AB-8F20-80EF69812EB7}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C49FB901-6C61-48D4-8885-CD4B94CA49CC}" name="OrderID" dataDxfId="36" totalsRowDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{6F5B641F-D34D-4BF0-BD99-B4B215FD6FA9}" name="Region" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="15" xr3:uid="{E2A25365-189D-48C0-BFAF-D4926D1D02EA}" name="Updated_Region" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{8377190E-9603-4D87-A476-ADEBFC3DC652}" name="Category" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{A4B6F6CD-A6EE-4E43-A3F3-4CD640FCFEF0}" name="sales" totalsRowFunction="custom" dataDxfId="28" totalsRowDxfId="27">
+    <tableColumn id="1" xr3:uid="{C49FB901-6C61-48D4-8885-CD4B94CA49CC}" name="OrderID" dataDxfId="36" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{6F5B641F-D34D-4BF0-BD99-B4B215FD6FA9}" name="Region" dataDxfId="35" totalsRowDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{E2A25365-189D-48C0-BFAF-D4926D1D02EA}" name="Updated_Region" dataDxfId="34" totalsRowDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{8377190E-9603-4D87-A476-ADEBFC3DC652}" name="Category" dataDxfId="33" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{A4B6F6CD-A6EE-4E43-A3F3-4CD640FCFEF0}" name="sales" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="11">
       <totalsRowFormula>SUBTOTAL(9,E2:E499)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{88C8845E-E9E6-4EB3-9534-3ABD853E188F}" name="sales_category" dataDxfId="26" totalsRowDxfId="25">
+    <tableColumn id="17" xr3:uid="{88C8845E-E9E6-4EB3-9534-3ABD853E188F}" name="sales_category" dataDxfId="31" totalsRowDxfId="10">
       <calculatedColumnFormula>IF(Table2[[#This Row],[sales]]&gt;3000,"High Sales",IF(Table2[[#This Row],[sales]]&gt;1000,"Medium Sales","Low" ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6C72F4F4-3AA4-4C07-B02D-E31D4FA9D807}" name="discount" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{EE41DADB-47D4-4FF1-9808-AE345B99EB94}" name="quantity" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{C8E77239-8BEF-4765-BC91-E801E93C50FC}" name="order_date" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{CE6E3ACB-BB6F-45AB-B748-BBC80F57753D}" name="delivery_date" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{DB87E83D-2907-4A6E-A194-7D21A3F8D4B8}" name="customer_type" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{6E987BBB-89BF-49AC-B6AB-4A376A75455C}" name="payment_mode" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{117FB979-FF11-4DCA-A8D6-7C90B05D3BC0}" name="profit" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{542039C3-2CB1-449E-B0DA-DBBF3A1CD25D}" name="Updated_City" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{70F2593B-A7FC-422D-BFD4-CD44CB9986C1}" name="city" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{A7605BF9-AA70-4D8C-B408-81E017BBE3A7}" name="Discount_Category" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6C72F4F4-3AA4-4C07-B02D-E31D4FA9D807}" name="discount" dataDxfId="30" totalsRowDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{EE41DADB-47D4-4FF1-9808-AE345B99EB94}" name="quantity" dataDxfId="29" totalsRowDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{C8E77239-8BEF-4765-BC91-E801E93C50FC}" name="order_date" dataDxfId="28" totalsRowDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{CE6E3ACB-BB6F-45AB-B748-BBC80F57753D}" name="delivery_date" dataDxfId="27" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{DB87E83D-2907-4A6E-A194-7D21A3F8D4B8}" name="customer_type" dataDxfId="26" totalsRowDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{6E987BBB-89BF-49AC-B6AB-4A376A75455C}" name="payment_mode" dataDxfId="25" totalsRowDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{117FB979-FF11-4DCA-A8D6-7C90B05D3BC0}" name="profit" dataDxfId="24" totalsRowDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{542039C3-2CB1-449E-B0DA-DBBF3A1CD25D}" name="Updated_City" dataDxfId="23" totalsRowDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{70F2593B-A7FC-422D-BFD4-CD44CB9986C1}" name="city" dataDxfId="22" totalsRowDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{A7605BF9-AA70-4D8C-B408-81E017BBE3A7}" name="Discount_Category" dataDxfId="21" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3961,7 +4071,7 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="54" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -6842,8 +6952,12 @@
       </c>
       <c r="P48" s="36"/>
       <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
+      <c r="R48" s="80" t="s">
+        <v>660</v>
+      </c>
+      <c r="S48" s="80" t="s">
+        <v>594</v>
+      </c>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
@@ -6902,6 +7016,13 @@
       </c>
       <c r="P49" s="36"/>
       <c r="Q49" s="1"/>
+      <c r="R49" s="79" t="s">
+        <v>509</v>
+      </c>
+      <c r="S49" s="72">
+        <f>VLOOKUP(R49,Table2[],MATCH(S48,Table2[#Headers],0),FALSE)</f>
+        <v>3507.5</v>
+      </c>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
@@ -47450,10 +47571,10 @@
       <c r="Y1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="top10" dxfId="4" priority="3" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="3" priority="4" rank="10"/>
+    <cfRule type="top10" dxfId="20" priority="3" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="19" priority="4" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
     <cfRule type="colorScale" priority="5">
@@ -47468,15 +47589,162 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R49" xr:uid="{24F88F4C-EBC9-4446-AC5E-B31E9EB34AF8}">
+      <formula1>$A$2:$A$499</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C65918F-A155-4CA3-98DF-45D9AF3C42CC}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>588</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B004292-5FE2-4460-87B7-22DCD9FDE941}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="25" t="s">
+        <v>588</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -47760,7 +48028,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{33AFE6E5-ED7F-4E10-8E86-F2AC6784377B}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{2D4C36CE-0C66-4840-AE6A-A4965A4B40AF}"/>
@@ -48593,12 +48861,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:B19">
     <sortCondition ref="A12:A19" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B12:B19">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
       <formula>65561.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
       <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48812,6 +49080,395 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E76B3D-8BFD-48AF-9FB7-35C69068B96D}">
+  <dimension ref="A2:G12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="27"/>
+      <c r="B2" s="69" t="s">
+        <v>693</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>694</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>695</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>696</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="69" t="s">
+        <v>697</v>
+      </c>
+      <c r="B3" s="27">
+        <v>100</v>
+      </c>
+      <c r="C3" s="27">
+        <v>585</v>
+      </c>
+      <c r="D3" s="27">
+        <v>333</v>
+      </c>
+      <c r="E3" s="27">
+        <v>745</v>
+      </c>
+      <c r="F3" s="27">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="69" t="s">
+        <v>698</v>
+      </c>
+      <c r="B4" s="27">
+        <v>100</v>
+      </c>
+      <c r="C4" s="27">
+        <v>500</v>
+      </c>
+      <c r="D4" s="27">
+        <v>600</v>
+      </c>
+      <c r="E4" s="27">
+        <v>700</v>
+      </c>
+      <c r="F4" s="27">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="69" t="s">
+        <v>594</v>
+      </c>
+      <c r="B5" s="27">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="27">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="27">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="27">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="27">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="69" t="s">
+        <v>699</v>
+      </c>
+      <c r="B6" s="27">
+        <v>400</v>
+      </c>
+      <c r="C6" s="27">
+        <v>500</v>
+      </c>
+      <c r="D6" s="27">
+        <v>300</v>
+      </c>
+      <c r="E6" s="27">
+        <v>300</v>
+      </c>
+      <c r="F6" s="27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F8" s="66" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="68" t="s">
+        <v>700</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>696</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>700</v>
+      </c>
+      <c r="G9" s="67" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="68" t="s">
+        <v>594</v>
+      </c>
+      <c r="C10" s="27">
+        <f>HLOOKUP($C$9,$B$2:$F$6,MATCH(B10,$A$2:$A$6,0),FALSE)</f>
+        <v>6000</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>594</v>
+      </c>
+      <c r="G10" s="27">
+        <f>VLOOKUP(F10,$A$3:$F$6,MATCH($G$9,$A$2:$F$2,0),FALSE)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="68" t="s">
+        <v>698</v>
+      </c>
+      <c r="C11" s="27">
+        <f t="shared" ref="C11:C12" si="0">HLOOKUP($C$9,$B$2:$F$6,MATCH(B11,$A$2:$A$6,0),FALSE)</f>
+        <v>700</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>699</v>
+      </c>
+      <c r="G11" s="27">
+        <f>VLOOKUP(F11,$A$3:$F$6,MATCH($G$9,$A$2:$F$2,0),FALSE)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="68" t="s">
+        <v>699</v>
+      </c>
+      <c r="C12" s="27">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA493DB5-ACA7-4A9B-8129-29A1710E0B65}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11583066-D15A-4395-8FBA-CD7901E37180}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="3" width="8.7265625" style="27"/>
+    <col min="4" max="4" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" style="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="73" t="s">
+        <v>702</v>
+      </c>
+      <c r="B1" s="70" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" s="70" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>706</v>
+      </c>
+      <c r="E1" s="70" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="74">
+        <v>55</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>708</v>
+      </c>
+      <c r="C2" s="27">
+        <v>4</v>
+      </c>
+      <c r="D2" s="77">
+        <v>46214</v>
+      </c>
+      <c r="E2" s="27">
+        <v>45</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>704</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="74">
+        <v>44</v>
+      </c>
+      <c r="B3" s="72" t="s">
+        <v>709</v>
+      </c>
+      <c r="C3" s="27">
+        <v>5</v>
+      </c>
+      <c r="D3" s="77">
+        <v>46215</v>
+      </c>
+      <c r="E3" s="27">
+        <v>55</v>
+      </c>
+      <c r="F3" s="71" t="s">
+        <v>705</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="74">
+        <v>34</v>
+      </c>
+      <c r="C4" s="27">
+        <v>3</v>
+      </c>
+      <c r="D4" s="77">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="74">
+        <v>43</v>
+      </c>
+      <c r="C5" s="27">
+        <v>7</v>
+      </c>
+      <c r="D5" s="77">
+        <v>46217</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5" t="b">
+        <f>AND(G5&gt;40,G5&lt;=75)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="75">
+        <v>56</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>710</v>
+      </c>
+      <c r="C6" s="76"/>
+      <c r="D6" s="77">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="75">
+        <v>34</v>
+      </c>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="77">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="75">
+        <v>45</v>
+      </c>
+      <c r="B8" s="76"/>
+      <c r="D8" s="77">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="75">
+        <v>33</v>
+      </c>
+      <c r="B9" s="76"/>
+      <c r="D9" s="77">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="75">
+        <v>45</v>
+      </c>
+      <c r="B10" s="76"/>
+      <c r="D10" s="77">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="75">
+        <v>12</v>
+      </c>
+      <c r="B11" s="76"/>
+      <c r="D11" s="77">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="75">
+        <v>60</v>
+      </c>
+      <c r="B12" s="76"/>
+      <c r="D12" s="77">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="75">
+        <v>34</v>
+      </c>
+      <c r="B13" s="76"/>
+      <c r="D13" s="77">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="75">
+        <v>68</v>
+      </c>
+      <c r="B14" s="76"/>
+    </row>
+  </sheetData>
+  <dataValidations disablePrompts="1" count="6">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Age Error" error="The entereed age is not in range." promptTitle="Age restrictions" prompt="Enter value between 18 to 60" sqref="A1:A1048576" xr:uid="{BAD46E2A-3963-4C03-A0F2-D168750AD8C5}">
+      <formula1>18</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Quantity Error" error="Entered quantity is not valid" promptTitle="Quantity" prompt="Enter quantity bewteen 2-10" sqref="C2:C1048576" xr:uid="{AAC7344D-190B-4C5A-AADE-B7EA05CFCBBE}">
+      <formula1>$G$2</formula1>
+      <formula2>$G$3</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{FE16BB8B-764A-4177-9779-6725BAF57D86}">
+      <formula1>46218</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{1FAEE3CF-54F4-4F54-BF8B-888E6AA8CCFA}">
+      <formula1>AND(E2&gt;40,E2&lt;=75)</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Incorrect OTP" error="You have entered incorrect OTP" promptTitle="OTP" prompt="Enter otp received(4 characters)" sqref="B3:B1048576" xr:uid="{EBFC523D-AA7A-43A2-B0E3-ACD119E7D74F}">
+      <formula1>4</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Incorrect OTP" error="You have entered incorrect OTP" promptTitle="OTP" prompt="Enter otp received(4 characters)" sqref="B2" xr:uid="{9431EEED-33C7-4867-8EEA-D79821CEF2E4}">
+      <formula1>4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9218A3-BABC-4C3F-8219-A1BE1DF8467C}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -48948,7 +49605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52549AE3-D95B-4E0A-B580-C470F614F2AF}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -49014,149 +49671,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C65918F-A155-4CA3-98DF-45D9AF3C42CC}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>588</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B004292-5FE2-4460-87B7-22DCD9FDE941}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>588</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\DSDA11\N322\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6D2148-BD7D-46A1-9899-41F0E4576B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28BCD7C-FDC1-45AE-8F8F-251922BD4C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2590,7 +2590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2714,10 +2714,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -2726,428 +2724,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="40">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3209,6 +2785,32 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3220,6 +2822,34 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3265,17 +2895,16 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3319,6 +2948,32 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3346,6 +3001,32 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3357,6 +3038,86 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3401,6 +3162,33 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
@@ -3413,6 +3201,32 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3456,6 +3270,32 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3467,6 +3307,32 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3511,6 +3377,32 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3522,6 +3414,32 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3565,6 +3483,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3592,6 +3536,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3603,6 +3573,34 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3702,26 +3700,26 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5BA5497F-DEC0-44AB-8F20-80EF69812EB7}" name="Table2" displayName="Table2" ref="A1:P500" totalsRowCount="1" headerRowDxfId="39" dataDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="A1:P499" xr:uid="{5BA5497F-DEC0-44AB-8F20-80EF69812EB7}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C49FB901-6C61-48D4-8885-CD4B94CA49CC}" name="OrderID" dataDxfId="36" totalsRowDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{6F5B641F-D34D-4BF0-BD99-B4B215FD6FA9}" name="Region" dataDxfId="35" totalsRowDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{E2A25365-189D-48C0-BFAF-D4926D1D02EA}" name="Updated_Region" dataDxfId="34" totalsRowDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{8377190E-9603-4D87-A476-ADEBFC3DC652}" name="Category" dataDxfId="33" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{A4B6F6CD-A6EE-4E43-A3F3-4CD640FCFEF0}" name="sales" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="11">
+    <tableColumn id="1" xr3:uid="{C49FB901-6C61-48D4-8885-CD4B94CA49CC}" name="OrderID" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{6F5B641F-D34D-4BF0-BD99-B4B215FD6FA9}" name="Region" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{E2A25365-189D-48C0-BFAF-D4926D1D02EA}" name="Updated_Region" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{8377190E-9603-4D87-A476-ADEBFC3DC652}" name="Category" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{A4B6F6CD-A6EE-4E43-A3F3-4CD640FCFEF0}" name="sales" totalsRowFunction="custom" dataDxfId="28" totalsRowDxfId="27">
       <totalsRowFormula>SUBTOTAL(9,E2:E499)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{88C8845E-E9E6-4EB3-9534-3ABD853E188F}" name="sales_category" dataDxfId="31" totalsRowDxfId="10">
+    <tableColumn id="17" xr3:uid="{88C8845E-E9E6-4EB3-9534-3ABD853E188F}" name="sales_category" dataDxfId="26" totalsRowDxfId="25">
       <calculatedColumnFormula>IF(Table2[[#This Row],[sales]]&gt;3000,"High Sales",IF(Table2[[#This Row],[sales]]&gt;1000,"Medium Sales","Low" ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6C72F4F4-3AA4-4C07-B02D-E31D4FA9D807}" name="discount" dataDxfId="30" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{EE41DADB-47D4-4FF1-9808-AE345B99EB94}" name="quantity" dataDxfId="29" totalsRowDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{C8E77239-8BEF-4765-BC91-E801E93C50FC}" name="order_date" dataDxfId="28" totalsRowDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{CE6E3ACB-BB6F-45AB-B748-BBC80F57753D}" name="delivery_date" dataDxfId="27" totalsRowDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{DB87E83D-2907-4A6E-A194-7D21A3F8D4B8}" name="customer_type" dataDxfId="26" totalsRowDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{6E987BBB-89BF-49AC-B6AB-4A376A75455C}" name="payment_mode" dataDxfId="25" totalsRowDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{117FB979-FF11-4DCA-A8D6-7C90B05D3BC0}" name="profit" dataDxfId="24" totalsRowDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{542039C3-2CB1-449E-B0DA-DBBF3A1CD25D}" name="Updated_City" dataDxfId="23" totalsRowDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{70F2593B-A7FC-422D-BFD4-CD44CB9986C1}" name="city" dataDxfId="22" totalsRowDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{A7605BF9-AA70-4D8C-B408-81E017BBE3A7}" name="Discount_Category" dataDxfId="21" totalsRowDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6C72F4F4-3AA4-4C07-B02D-E31D4FA9D807}" name="discount" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{EE41DADB-47D4-4FF1-9808-AE345B99EB94}" name="quantity" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{C8E77239-8BEF-4765-BC91-E801E93C50FC}" name="order_date" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{CE6E3ACB-BB6F-45AB-B748-BBC80F57753D}" name="delivery_date" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{DB87E83D-2907-4A6E-A194-7D21A3F8D4B8}" name="customer_type" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{6E987BBB-89BF-49AC-B6AB-4A376A75455C}" name="payment_mode" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{117FB979-FF11-4DCA-A8D6-7C90B05D3BC0}" name="profit" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{542039C3-2CB1-449E-B0DA-DBBF3A1CD25D}" name="Updated_City" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{70F2593B-A7FC-422D-BFD4-CD44CB9986C1}" name="city" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{A7605BF9-AA70-4D8C-B408-81E017BBE3A7}" name="Discount_Category" dataDxfId="6" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6952,10 +6950,10 @@
       </c>
       <c r="P48" s="36"/>
       <c r="Q48" s="1"/>
-      <c r="R48" s="80" t="s">
+      <c r="R48" s="78" t="s">
         <v>660</v>
       </c>
-      <c r="S48" s="80" t="s">
+      <c r="S48" s="78" t="s">
         <v>594</v>
       </c>
       <c r="T48" s="1"/>
@@ -7016,7 +7014,7 @@
       </c>
       <c r="P49" s="36"/>
       <c r="Q49" s="1"/>
-      <c r="R49" s="79" t="s">
+      <c r="R49" s="77" t="s">
         <v>509</v>
       </c>
       <c r="S49" s="72">
@@ -47573,8 +47571,8 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="top10" dxfId="20" priority="3" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="19" priority="4" rank="10"/>
+    <cfRule type="top10" dxfId="4" priority="3" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="3" priority="4" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
     <cfRule type="colorScale" priority="5">
@@ -47589,7 +47587,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48863,10 +48861,10 @@
   </sortState>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B12:B19">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>65561.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49294,7 +49292,7 @@
       <c r="C2" s="27">
         <v>4</v>
       </c>
-      <c r="D2" s="77">
+      <c r="D2" s="76">
         <v>46214</v>
       </c>
       <c r="E2" s="27">
@@ -49317,7 +49315,7 @@
       <c r="C3" s="27">
         <v>5</v>
       </c>
-      <c r="D3" s="77">
+      <c r="D3" s="76">
         <v>46215</v>
       </c>
       <c r="E3" s="27">
@@ -49337,7 +49335,7 @@
       <c r="C4" s="27">
         <v>3</v>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="76">
         <v>46216</v>
       </c>
     </row>
@@ -49348,7 +49346,7 @@
       <c r="C5" s="27">
         <v>7</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="76">
         <v>46217</v>
       </c>
       <c r="G5">
@@ -49363,11 +49361,10 @@
       <c r="A6" s="75">
         <v>56</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="72" t="s">
         <v>710</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="77">
+      <c r="D6" s="76">
         <v>46218</v>
       </c>
     </row>
@@ -49375,9 +49372,7 @@
       <c r="A7" s="75">
         <v>34</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="77">
+      <c r="D7" s="76">
         <v>46219</v>
       </c>
     </row>
@@ -49385,8 +49380,7 @@
       <c r="A8" s="75">
         <v>45</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="D8" s="77">
+      <c r="D8" s="76">
         <v>46220</v>
       </c>
     </row>
@@ -49394,8 +49388,7 @@
       <c r="A9" s="75">
         <v>33</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="D9" s="77">
+      <c r="D9" s="76">
         <v>46221</v>
       </c>
     </row>
@@ -49403,8 +49396,7 @@
       <c r="A10" s="75">
         <v>45</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="D10" s="77">
+      <c r="D10" s="76">
         <v>46163</v>
       </c>
     </row>
@@ -49412,8 +49404,7 @@
       <c r="A11" s="75">
         <v>12</v>
       </c>
-      <c r="B11" s="76"/>
-      <c r="D11" s="77">
+      <c r="D11" s="76">
         <v>46164</v>
       </c>
     </row>
@@ -49421,8 +49412,7 @@
       <c r="A12" s="75">
         <v>60</v>
       </c>
-      <c r="B12" s="76"/>
-      <c r="D12" s="77">
+      <c r="D12" s="76">
         <v>46165</v>
       </c>
     </row>
@@ -49430,8 +49420,7 @@
       <c r="A13" s="75">
         <v>34</v>
       </c>
-      <c r="B13" s="76"/>
-      <c r="D13" s="77">
+      <c r="D13" s="76">
         <v>46166</v>
       </c>
     </row>
@@ -49439,7 +49428,6 @@
       <c r="A14" s="75">
         <v>68</v>
       </c>
-      <c r="B14" s="76"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="6">
